--- a/report-saved-shipments.xlsx
+++ b/report-saved-shipments.xlsx
@@ -11,15 +11,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="42">
   <si>
     <t>Shipment Report</t>
   </si>
   <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Skyinventories</t>
+  </si>
+  <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>02 Apr 2026, 09:11</t>
+    <t>02 Apr 2026, 09:24</t>
   </si>
   <si>
     <t>Mode</t>
@@ -88,7 +94,7 @@
     <t>Test123</t>
   </si>
   <si>
-    <t>received</t>
+    <t>Received</t>
   </si>
   <si>
     <t>test admin</t>
@@ -100,7 +106,7 @@
     <t>test@gmail.com</t>
   </si>
   <si>
-    <t>greater_accra</t>
+    <t>Greater Accra</t>
   </si>
   <si>
     <t>Test partner</t>
@@ -125,6 +131,12 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>123.000</t>
   </si>
 </sst>
 </file>
@@ -134,7 +146,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -155,8 +167,12 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF0F172A"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,6 +192,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -206,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -231,6 +252,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -572,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -645,100 +673,156 @@
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="8" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="B8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="I8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="K8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="L8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="O7" s="7" t="s">
+      <c r="M8" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="N8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="O8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="9">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="9">
         <v>123</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="M9" s="5" t="s">
         <v>37</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
